--- a/logs/duplicate_records.xlsx
+++ b/logs/duplicate_records.xlsx
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">

--- a/logs/duplicate_records.xlsx
+++ b/logs/duplicate_records.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4833,7 +4833,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SERENITY 1 (9060247) - Bulk Carrier, Broken Up, 28458 dwt, 17430gt</t>
+          <t>SERENITY 1</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5355,7 +5355,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5471,7 +5471,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5500,7 +5500,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>RADA (9213301) - Crude Oil Tanker, Broken Up, 112201 dwt, 62385gt</t>
+          <t>RADA</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
